--- a/design/tables/StaffBranch.xlsx
+++ b/design/tables/StaffBranch.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StaffBranch" sheetId="1" r:id="R36ba332ed4324e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StaffBranch" sheetId="1" r:id="Rd48072bcde1f438f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -27,8 +27,18 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF243C32"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -45,6 +55,11 @@
         <x:fgColor rgb="FF35584D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -52,7 +67,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -75,6 +90,17 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -297,6 +323,19 @@
     <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="42" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="24" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="24" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="24" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="24" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="24" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="24" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="24" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="24" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="24" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="24" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="24" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="48" customHeight="1">
@@ -357,6 +396,45 @@
       <x:c r="S1" s="6" t="str">
         <x:v>进化形态键</x:v>
       </x:c>
+      <x:c r="T1" t="str">
+        <x:v>穿透长度</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>穿透半宽</x:v>
+      </x:c>
+      <x:c r="V1" t="str">
+        <x:v>穿透伤害比例</x:v>
+      </x:c>
+      <x:c r="W1" t="str">
+        <x:v>电链总目标数</x:v>
+      </x:c>
+      <x:c r="X1" t="str">
+        <x:v>电链连接半径</x:v>
+      </x:c>
+      <x:c r="Y1" t="str">
+        <x:v>电链逐跳伤害比例</x:v>
+      </x:c>
+      <x:c r="Z1" t="str">
+        <x:v>每秒灼烧最终伤害</x:v>
+      </x:c>
+      <x:c r="AA1" t="str">
+        <x:v>灼烧时长秒</x:v>
+      </x:c>
+      <x:c r="AB1" t="str">
+        <x:v>标记直击伤害倍率</x:v>
+      </x:c>
+      <x:c r="AC1" t="str">
+        <x:v>标记持续秒</x:v>
+      </x:c>
+      <x:c r="AD1" t="str">
+        <x:v>弹道色</x:v>
+      </x:c>
+      <x:c r="AE1" t="str">
+        <x:v>弹道速度</x:v>
+      </x:c>
+      <x:c r="AF1" t="str">
+        <x:v>多目标弯曲幅度</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="48" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -414,6 +492,45 @@
         <x:v>client</x:v>
       </x:c>
       <x:c r="S2" s="6" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="T2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="V2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="W2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="X2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="Y2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="Z2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AA2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AB2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AC2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AD2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AE2" t="str">
+        <x:v>client</x:v>
+      </x:c>
+      <x:c r="AF2" t="str">
         <x:v>client</x:v>
       </x:c>
     </x:row>
@@ -475,6 +592,45 @@
       <x:c r="S3" s="6" t="str">
         <x:v>string</x:v>
       </x:c>
+      <x:c r="T3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="U3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="V3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="W3" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="X3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Y3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Z3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AA3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AB3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AC3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AD3" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="AE3" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AF3" t="str">
+        <x:v>float</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="48" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -534,6 +690,45 @@
       <x:c r="S4" s="6" t="str">
         <x:v>进化形态键</x:v>
       </x:c>
+      <x:c r="T4" t="str">
+        <x:v>穿透长度</x:v>
+      </x:c>
+      <x:c r="U4" t="str">
+        <x:v>穿透半宽</x:v>
+      </x:c>
+      <x:c r="V4" t="str">
+        <x:v>穿透伤害比例</x:v>
+      </x:c>
+      <x:c r="W4" t="str">
+        <x:v>电链总目标数</x:v>
+      </x:c>
+      <x:c r="X4" t="str">
+        <x:v>电链连接半径</x:v>
+      </x:c>
+      <x:c r="Y4" t="str">
+        <x:v>电链逐跳伤害比例</x:v>
+      </x:c>
+      <x:c r="Z4" t="str">
+        <x:v>每秒灼烧最终伤害</x:v>
+      </x:c>
+      <x:c r="AA4" t="str">
+        <x:v>灼烧时长秒</x:v>
+      </x:c>
+      <x:c r="AB4" t="str">
+        <x:v>标记直击伤害倍率</x:v>
+      </x:c>
+      <x:c r="AC4" t="str">
+        <x:v>标记持续秒</x:v>
+      </x:c>
+      <x:c r="AD4" t="str">
+        <x:v>弹道色</x:v>
+      </x:c>
+      <x:c r="AE4" t="str">
+        <x:v>弹道速度</x:v>
+      </x:c>
+      <x:c r="AF4" t="str">
+        <x:v>多目标弯曲幅度</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="48" customHeight="1">
       <x:c r="A5" s="7" t="str">
@@ -593,359 +788,1612 @@
       <x:c r="S5" s="7" t="str">
         <x:v>formKey</x:v>
       </x:c>
+      <x:c r="T5" t="str">
+        <x:v>pierceLength</x:v>
+      </x:c>
+      <x:c r="U5" t="str">
+        <x:v>pierceWidth</x:v>
+      </x:c>
+      <x:c r="V5" t="str">
+        <x:v>pierceRatio</x:v>
+      </x:c>
+      <x:c r="W5" t="str">
+        <x:v>chainCount</x:v>
+      </x:c>
+      <x:c r="X5" t="str">
+        <x:v>chainRadius</x:v>
+      </x:c>
+      <x:c r="Y5" t="str">
+        <x:v>chainRatio</x:v>
+      </x:c>
+      <x:c r="Z5" t="str">
+        <x:v>burnDamage</x:v>
+      </x:c>
+      <x:c r="AA5" t="str">
+        <x:v>burnSeconds</x:v>
+      </x:c>
+      <x:c r="AB5" t="str">
+        <x:v>markRatio</x:v>
+      </x:c>
+      <x:c r="AC5" t="str">
+        <x:v>markSeconds</x:v>
+      </x:c>
+      <x:c r="AD5" t="str">
+        <x:v>shotColor</x:v>
+      </x:c>
+      <x:c r="AE5" t="str">
+        <x:v>shotSpeed</x:v>
+      </x:c>
+      <x:c r="AF5" t="str">
+        <x:v>laneBend</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="48" customHeight="1">
-      <x:c r="A6" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="A6" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
         <x:v>sprout_heavy</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="str">
+      <x:c r="C6" s="11" t="str">
         <x:v>sprout</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="11" t="str">
         <x:v>branch.sprout_heavy.name</x:v>
       </x:c>
-      <x:c r="E6" s="8" t="n">
+      <x:c r="E6" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="n">
+      <x:c r="F6" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G6" s="8" t="n">
+      <x:c r="G6" s="11" t="n">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="H6" s="8" t="n">
+      <x:c r="H6" s="11" t="n">
         <x:v>0.96</x:v>
       </x:c>
-      <x:c r="I6" s="8" t="n">
+      <x:c r="I6" s="11" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="J6" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K6" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L6" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M6" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N6" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O6" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P6" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q6" s="8" t="n">
+      <x:c r="J6" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M6" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O6" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q6" s="11" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="R6" s="8" t="str">
+      <x:c r="R6" s="11" t="str">
         <x:v>sprout</x:v>
       </x:c>
-      <x:c r="S6" s="8" t="str">
+      <x:c r="S6" s="11" t="str">
         <x:v>sprout_heavy</x:v>
+      </x:c>
+      <x:c r="T6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB6" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC6" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD6" s="13" t="str">
+        <x:v>#ffe072</x:v>
+      </x:c>
+      <x:c r="AE6" s="13" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="AF6" s="13" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="48" customHeight="1">
-      <x:c r="A7" s="8" t="n">
+      <x:c r="A7" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="str">
+      <x:c r="B7" s="11" t="str">
         <x:v>sprout_burst</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="str">
+      <x:c r="C7" s="11" t="str">
         <x:v>sprout</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="str">
+      <x:c r="D7" s="11" t="str">
         <x:v>branch.sprout_burst.name</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="n">
+      <x:c r="E7" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="n">
+      <x:c r="F7" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="n">
+      <x:c r="G7" s="11" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H7" s="8" t="n">
+      <x:c r="H7" s="11" t="n">
         <x:v>0.72</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="n">
+      <x:c r="I7" s="11" t="n">
         <x:v>106</x:v>
       </x:c>
-      <x:c r="J7" s="8" t="n">
+      <x:c r="J7" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K7" s="8" t="n">
+      <x:c r="K7" s="11" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="L7" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M7" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N7" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O7" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q7" s="8" t="n">
+      <x:c r="L7" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M7" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N7" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O7" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q7" s="11" t="n">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="R7" s="8" t="str">
+      <x:c r="R7" s="11" t="str">
         <x:v>sprout</x:v>
       </x:c>
-      <x:c r="S7" s="8" t="str">
+      <x:c r="S7" s="11" t="str">
         <x:v>sprout_burst</x:v>
+      </x:c>
+      <x:c r="T7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB7" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC7" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD7" s="13" t="str">
+        <x:v>#ffe072</x:v>
+      </x:c>
+      <x:c r="AE7" s="13" t="n">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="AF7" s="13" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="48" customHeight="1">
-      <x:c r="A8" s="8" t="n">
+      <x:c r="A8" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="str">
+      <x:c r="B8" s="11" t="str">
         <x:v>frost_deep</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="str">
+      <x:c r="C8" s="11" t="str">
         <x:v>frost</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="str">
+      <x:c r="D8" s="11" t="str">
         <x:v>branch.frost_deep.name</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="n">
+      <x:c r="E8" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="n">
+      <x:c r="F8" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="n">
+      <x:c r="G8" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H8" s="8" t="n">
+      <x:c r="H8" s="11" t="n">
         <x:v>1.05</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="n">
+      <x:c r="I8" s="11" t="n">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="J8" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K8" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L8" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M8" s="8" t="n">
+      <x:c r="J8" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K8" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M8" s="11" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="N8" s="8" t="n">
+      <x:c r="N8" s="11" t="n">
         <x:v>1.6</x:v>
       </x:c>
-      <x:c r="O8" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q8" s="8" t="n">
+      <x:c r="O8" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q8" s="11" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="R8" s="8" t="str">
+      <x:c r="R8" s="11" t="str">
         <x:v>frost</x:v>
       </x:c>
-      <x:c r="S8" s="8" t="str">
+      <x:c r="S8" s="11" t="str">
         <x:v>frost_deep</x:v>
+      </x:c>
+      <x:c r="T8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB8" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC8" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD8" s="13" t="str">
+        <x:v>#e8f8ff</x:v>
+      </x:c>
+      <x:c r="AE8" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="AF8" s="13" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="48" customHeight="1">
-      <x:c r="A9" s="8" t="n">
+      <x:c r="A9" s="11" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="str">
+      <x:c r="B9" s="11" t="str">
         <x:v>frost_dual</x:v>
       </x:c>
-      <x:c r="C9" s="8" t="str">
+      <x:c r="C9" s="11" t="str">
         <x:v>frost</x:v>
       </x:c>
-      <x:c r="D9" s="8" t="str">
+      <x:c r="D9" s="11" t="str">
         <x:v>branch.frost_dual.name</x:v>
       </x:c>
-      <x:c r="E9" s="8" t="n">
+      <x:c r="E9" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F9" s="8" t="n">
+      <x:c r="F9" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G9" s="8" t="n">
+      <x:c r="G9" s="11" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H9" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I9" s="8" t="n">
+      <x:c r="H9" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="n">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="J9" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K9" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L9" s="8" t="n">
+      <x:c r="J9" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K9" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="M9" s="8" t="n">
+      <x:c r="M9" s="11" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="N9" s="8" t="n">
+      <x:c r="N9" s="11" t="n">
         <x:v>1.3</x:v>
       </x:c>
-      <x:c r="O9" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P9" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q9" s="8" t="n">
+      <x:c r="O9" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P9" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q9" s="11" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="R9" s="8" t="str">
+      <x:c r="R9" s="11" t="str">
         <x:v>frost</x:v>
       </x:c>
-      <x:c r="S9" s="8" t="str">
+      <x:c r="S9" s="11" t="str">
         <x:v>frost_dual</x:v>
+      </x:c>
+      <x:c r="T9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB9" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC9" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD9" s="13" t="str">
+        <x:v>#e8f8ff</x:v>
+      </x:c>
+      <x:c r="AE9" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="AF9" s="13" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="48" customHeight="1">
-      <x:c r="A10" s="8" t="n">
+      <x:c r="A10" s="11" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B10" s="8" t="str">
+      <x:c r="B10" s="11" t="str">
         <x:v>bloom_focus</x:v>
       </x:c>
-      <x:c r="C10" s="8" t="str">
+      <x:c r="C10" s="11" t="str">
         <x:v>bloom</x:v>
       </x:c>
-      <x:c r="D10" s="8" t="str">
+      <x:c r="D10" s="11" t="str">
         <x:v>branch.bloom_focus.name</x:v>
       </x:c>
-      <x:c r="E10" s="8" t="n">
+      <x:c r="E10" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F10" s="8" t="n">
+      <x:c r="F10" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G10" s="8" t="n">
+      <x:c r="G10" s="11" t="n">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="H10" s="8" t="n">
+      <x:c r="H10" s="11" t="n">
         <x:v>1.4</x:v>
       </x:c>
-      <x:c r="I10" s="8" t="n">
+      <x:c r="I10" s="11" t="n">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="J10" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K10" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L10" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M10" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N10" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O10" s="8" t="n">
+      <x:c r="J10" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M10" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N10" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O10" s="11" t="n">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="P10" s="8" t="n">
+      <x:c r="P10" s="11" t="n">
         <x:v>0.45</x:v>
       </x:c>
-      <x:c r="Q10" s="8" t="n">
+      <x:c r="Q10" s="11" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="R10" s="8" t="str">
+      <x:c r="R10" s="11" t="str">
         <x:v>bloom</x:v>
       </x:c>
-      <x:c r="S10" s="8" t="str">
+      <x:c r="S10" s="11" t="str">
         <x:v>bloom_focus</x:v>
+      </x:c>
+      <x:c r="T10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB10" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC10" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD10" s="13" t="str">
+        <x:v>#ffbd72</x:v>
+      </x:c>
+      <x:c r="AE10" s="13" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AF10" s="13" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="48" customHeight="1">
-      <x:c r="A11" s="8" t="n">
+      <x:c r="A11" s="11" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B11" s="8" t="str">
+      <x:c r="B11" s="11" t="str">
         <x:v>bloom_wide</x:v>
       </x:c>
-      <x:c r="C11" s="8" t="str">
+      <x:c r="C11" s="11" t="str">
         <x:v>bloom</x:v>
       </x:c>
-      <x:c r="D11" s="8" t="str">
+      <x:c r="D11" s="11" t="str">
         <x:v>branch.bloom_wide.name</x:v>
       </x:c>
-      <x:c r="E11" s="8" t="n">
+      <x:c r="E11" s="11" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F11" s="8" t="n">
+      <x:c r="F11" s="11" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G11" s="8" t="n">
+      <x:c r="G11" s="11" t="n">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="H11" s="8" t="n">
+      <x:c r="H11" s="11" t="n">
         <x:v>1.2</x:v>
       </x:c>
-      <x:c r="I11" s="8" t="n">
+      <x:c r="I11" s="11" t="n">
         <x:v>118</x:v>
       </x:c>
-      <x:c r="J11" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L11" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M11" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="N11" s="8" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="O11" s="8" t="n">
+      <x:c r="J11" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M11" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N11" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O11" s="11" t="n">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="P11" s="8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="Q11" s="8" t="n">
+      <x:c r="P11" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q11" s="11" t="n">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="R11" s="8" t="str">
+      <x:c r="R11" s="11" t="str">
         <x:v>bloom</x:v>
       </x:c>
-      <x:c r="S11" s="8" t="str">
+      <x:c r="S11" s="11" t="str">
         <x:v>bloom_wide</x:v>
+      </x:c>
+      <x:c r="T11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB11" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD11" s="13" t="str">
+        <x:v>#ffbd72</x:v>
+      </x:c>
+      <x:c r="AE11" s="13" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="AF11" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="48" customHeight="1">
+      <x:c r="A12" s="13" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="str">
+        <x:v>scope</x:v>
+      </x:c>
+      <x:c r="D12" s="13" t="str">
+        <x:v>branch.scope_precision.name</x:v>
+      </x:c>
+      <x:c r="E12" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F12" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G12" s="13" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H12" s="13" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="I12" s="13" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J12" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M12" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q12" s="13" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="R12" s="13" t="str">
+        <x:v>scope</x:v>
+      </x:c>
+      <x:c r="S12" s="13" t="str">
+        <x:v>scope_precision</x:v>
+      </x:c>
+      <x:c r="T12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB12" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD12" s="13" t="str">
+        <x:v>#ffd27a</x:v>
+      </x:c>
+      <x:c r="AE12" s="13" t="n">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="AF12" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="48" customHeight="1">
+      <x:c r="A13" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B13" s="13" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="C13" s="13" t="str">
+        <x:v>scope</x:v>
+      </x:c>
+      <x:c r="D13" s="13" t="str">
+        <x:v>branch.scope_pierce.name</x:v>
+      </x:c>
+      <x:c r="E13" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F13" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G13" s="13" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H13" s="13" t="n">
+        <x:v>1.36</x:v>
+      </x:c>
+      <x:c r="I13" s="13" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J13" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M13" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q13" s="13" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="R13" s="13" t="str">
+        <x:v>scope</x:v>
+      </x:c>
+      <x:c r="S13" s="13" t="str">
+        <x:v>scope_pierce</x:v>
+      </x:c>
+      <x:c r="T13" s="13" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="U13" s="13" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="V13" s="13" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="W13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB13" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD13" s="13" t="str">
+        <x:v>#9adc91</x:v>
+      </x:c>
+      <x:c r="AE13" s="13" t="n">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="AF13" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="48" customHeight="1">
+      <x:c r="A14" s="13" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="13" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="C14" s="13" t="str">
+        <x:v>spark</x:v>
+      </x:c>
+      <x:c r="D14" s="13" t="str">
+        <x:v>branch.spark_focus.name</x:v>
+      </x:c>
+      <x:c r="E14" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F14" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G14" s="13" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="H14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="13" t="n">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="J14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q14" s="13" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="R14" s="13" t="str">
+        <x:v>spark</x:v>
+      </x:c>
+      <x:c r="S14" s="13" t="str">
+        <x:v>spark_focus</x:v>
+      </x:c>
+      <x:c r="T14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W14" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="X14" s="13" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="Y14" s="13" t="n">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="Z14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB14" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD14" s="13" t="str">
+        <x:v>#ffc75c</x:v>
+      </x:c>
+      <x:c r="AE14" s="13" t="n">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="AF14" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
+      <x:c r="A15" s="13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="13" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="C15" s="13" t="str">
+        <x:v>spark</x:v>
+      </x:c>
+      <x:c r="D15" s="13" t="str">
+        <x:v>branch.spark_chain.name</x:v>
+      </x:c>
+      <x:c r="E15" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F15" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G15" s="13" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H15" s="13" t="n">
+        <x:v>1.08</x:v>
+      </x:c>
+      <x:c r="I15" s="13" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J15" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M15" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q15" s="13" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="R15" s="13" t="str">
+        <x:v>spark</x:v>
+      </x:c>
+      <x:c r="S15" s="13" t="str">
+        <x:v>spark_chain</x:v>
+      </x:c>
+      <x:c r="T15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W15" s="13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X15" s="13" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="Y15" s="13" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="Z15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB15" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD15" s="13" t="str">
+        <x:v>#c4b5ff</x:v>
+      </x:c>
+      <x:c r="AE15" s="13" t="n">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="AF15" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
+      <x:c r="A16" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="13" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="C16" s="13" t="str">
+        <x:v>ember</x:v>
+      </x:c>
+      <x:c r="D16" s="13" t="str">
+        <x:v>branch.ember_scorch.name</x:v>
+      </x:c>
+      <x:c r="E16" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F16" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G16" s="13" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I16" s="13" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q16" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="R16" s="13" t="str">
+        <x:v>ember</x:v>
+      </x:c>
+      <x:c r="S16" s="13" t="str">
+        <x:v>ember_scorch</x:v>
+      </x:c>
+      <x:c r="T16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z16" s="13" t="n">
+        <x:v>22.5</x:v>
+      </x:c>
+      <x:c r="AA16" s="13" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="AB16" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD16" s="13" t="str">
+        <x:v>#ff9452</x:v>
+      </x:c>
+      <x:c r="AE16" s="13" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="AF16" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="48" customHeight="1">
+      <x:c r="A17" s="13" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="13" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="C17" s="13" t="str">
+        <x:v>ember</x:v>
+      </x:c>
+      <x:c r="D17" s="13" t="str">
+        <x:v>branch.ember_burst.name</x:v>
+      </x:c>
+      <x:c r="E17" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F17" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G17" s="13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H17" s="13" t="n">
+        <x:v>1.12</x:v>
+      </x:c>
+      <x:c r="I17" s="13" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="J17" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M17" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O17" s="13" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="P17" s="13" t="n">
+        <x:v>0.7</x:v>
+      </x:c>
+      <x:c r="Q17" s="13" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="R17" s="13" t="str">
+        <x:v>ember</x:v>
+      </x:c>
+      <x:c r="S17" s="13" t="str">
+        <x:v>ember_burst</x:v>
+      </x:c>
+      <x:c r="T17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z17" s="13" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="AA17" s="13" t="n">
+        <x:v>2.2</x:v>
+      </x:c>
+      <x:c r="AB17" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD17" s="13" t="str">
+        <x:v>#ffcd70</x:v>
+      </x:c>
+      <x:c r="AE17" s="13" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="AF17" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="48" customHeight="1">
+      <x:c r="A18" s="13" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="13" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="C18" s="13" t="str">
+        <x:v>mint</x:v>
+      </x:c>
+      <x:c r="D18" s="13" t="str">
+        <x:v>branch.mint_focus.name</x:v>
+      </x:c>
+      <x:c r="E18" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F18" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G18" s="13" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H18" s="13" t="n">
+        <x:v>0.94</x:v>
+      </x:c>
+      <x:c r="I18" s="13" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="J18" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M18" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q18" s="13" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="R18" s="13" t="str">
+        <x:v>mint</x:v>
+      </x:c>
+      <x:c r="S18" s="13" t="str">
+        <x:v>mint_focus</x:v>
+      </x:c>
+      <x:c r="T18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB18" s="13" t="n">
+        <x:v>1.4</x:v>
+      </x:c>
+      <x:c r="AC18" s="13" t="n">
+        <x:v>2.4</x:v>
+      </x:c>
+      <x:c r="AD18" s="13" t="str">
+        <x:v>#67dba4</x:v>
+      </x:c>
+      <x:c r="AE18" s="13" t="n">
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="AF18" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="48" customHeight="1">
+      <x:c r="A19" s="13" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="13" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="C19" s="13" t="str">
+        <x:v>mint</x:v>
+      </x:c>
+      <x:c r="D19" s="13" t="str">
+        <x:v>branch.mint_dual.name</x:v>
+      </x:c>
+      <x:c r="E19" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F19" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G19" s="13" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H19" s="13" t="n">
+        <x:v>1.05</x:v>
+      </x:c>
+      <x:c r="I19" s="13" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J19" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M19" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q19" s="13" t="n">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="R19" s="13" t="str">
+        <x:v>mint</x:v>
+      </x:c>
+      <x:c r="S19" s="13" t="str">
+        <x:v>mint_dual</x:v>
+      </x:c>
+      <x:c r="T19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB19" s="13" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="AC19" s="13" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="AD19" s="13" t="str">
+        <x:v>#b8eaca</x:v>
+      </x:c>
+      <x:c r="AE19" s="13" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="AF19" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="48" customHeight="1">
+      <x:c r="A20" s="13" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" s="13" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="C20" s="13" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D20" s="13" t="str">
+        <x:v>branch.fan_spread.name</x:v>
+      </x:c>
+      <x:c r="E20" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F20" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G20" s="13" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H20" s="13" t="n">
+        <x:v>1.08</x:v>
+      </x:c>
+      <x:c r="I20" s="13" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="J20" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20" s="13" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="M20" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q20" s="13" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="R20" s="13" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="S20" s="13" t="str">
+        <x:v>fan_spread</x:v>
+      </x:c>
+      <x:c r="T20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB20" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC20" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD20" s="13" t="str">
+        <x:v>#a1dfff</x:v>
+      </x:c>
+      <x:c r="AE20" s="13" t="n">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="AF20" s="13" t="n">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="48" customHeight="1">
+      <x:c r="A21" s="13" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="13" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="C21" s="13" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="D21" s="13" t="str">
+        <x:v>branch.fan_volley.name</x:v>
+      </x:c>
+      <x:c r="E21" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F21" s="13" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G21" s="13" t="n">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H21" s="13" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="I21" s="13" t="n">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="J21" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K21" s="13" t="n">
+        <x:v>0.14</x:v>
+      </x:c>
+      <x:c r="L21" s="13" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="M21" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P21" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Q21" s="13" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="R21" s="13" t="str">
+        <x:v>fan</x:v>
+      </x:c>
+      <x:c r="S21" s="13" t="str">
+        <x:v>fan_volley</x:v>
+      </x:c>
+      <x:c r="T21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="X21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Z21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AB21" s="13" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC21" s="13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AD21" s="13" t="str">
+        <x:v>#65c6f2</x:v>
+      </x:c>
+      <x:c r="AE21" s="13" t="n">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="AF21" s="13" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
